--- a/client/public/templates/spec-template-en.xlsx
+++ b/client/public/templates/spec-template-en.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pmerz\AppData\Roaming\ELO Digital Office\Aulbach_ab_2018\94\checkout\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mwatzal\Downloads\Development-Suit-main\Development-Suit-main\client\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18037964-1109-4554-ABB4-36439DE18F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{36CDD59F-9427-4E43-A607-459D1D82D957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -955,18 +955,308 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -977,303 +1267,13 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1297,35 +1297,35 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1333,7 +1333,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1345,7 +1345,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1357,27 +1357,27 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp28.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1389,7 +1389,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1397,7 +1397,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1413,7 +1413,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1421,7 +1421,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp39.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1433,11 +1433,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp41.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp42.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp43.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4773,195 +4773,195 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="88" t="s">
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="63" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="85" t="s">
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="61" t="s">
         <v>69</v>
       </c>
-      <c r="K1" s="85"/>
+      <c r="K1" s="61"/>
     </row>
     <row r="2" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="87"/>
-      <c r="B2" s="87"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="87"/>
+      <c r="A2" s="62"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
     </row>
     <row r="4" spans="1:11" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="86"/>
-      <c r="B4" s="86"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="54" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="64" t="s">
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="99" t="s">
         <v>71</v>
       </c>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="99"/>
       <c r="I7" s="20"/>
-      <c r="J7" s="100"/>
-      <c r="K7" s="100"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
+      <c r="B8" s="73"/>
+      <c r="C8" s="73"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="115"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="115"/>
+      <c r="H8" s="115"/>
+      <c r="I8" s="115"/>
+      <c r="J8" s="115"/>
+      <c r="K8" s="115"/>
     </row>
     <row r="9" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
+      <c r="A9" s="73"/>
+      <c r="B9" s="73"/>
+      <c r="C9" s="73"/>
+      <c r="D9" s="115"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="115"/>
+      <c r="H9" s="115"/>
+      <c r="I9" s="115"/>
+      <c r="J9" s="115"/>
+      <c r="K9" s="115"/>
     </row>
     <row r="10" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="28"/>
+      <c r="A10" s="73"/>
+      <c r="B10" s="73"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="115"/>
+      <c r="E10" s="115"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="115"/>
+      <c r="H10" s="115"/>
+      <c r="I10" s="115"/>
+      <c r="J10" s="115"/>
+      <c r="K10" s="115"/>
     </row>
     <row r="11" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="27"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="28"/>
-      <c r="K11" s="28"/>
+      <c r="A11" s="73"/>
+      <c r="B11" s="73"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="115"/>
+      <c r="E11" s="115"/>
+      <c r="F11" s="115"/>
+      <c r="G11" s="115"/>
+      <c r="H11" s="115"/>
+      <c r="I11" s="115"/>
+      <c r="J11" s="115"/>
+      <c r="K11" s="115"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28"/>
+      <c r="B12" s="73"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="115"/>
+      <c r="E12" s="115"/>
+      <c r="F12" s="115"/>
+      <c r="G12" s="115"/>
+      <c r="H12" s="115"/>
+      <c r="I12" s="115"/>
+      <c r="J12" s="115"/>
+      <c r="K12" s="115"/>
     </row>
     <row r="13" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
+      <c r="B13" s="73"/>
+      <c r="C13" s="73"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="115"/>
+      <c r="H13" s="115"/>
+      <c r="I13" s="115"/>
+      <c r="J13" s="115"/>
+      <c r="K13" s="115"/>
     </row>
     <row r="14" spans="1:11" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="18"/>
@@ -4977,579 +4977,579 @@
       <c r="K14" s="19"/>
     </row>
     <row r="15" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="116" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
+      <c r="B15" s="116"/>
+      <c r="C15" s="116"/>
+      <c r="D15" s="115"/>
+      <c r="E15" s="115"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="115"/>
+      <c r="H15" s="115"/>
+      <c r="I15" s="115"/>
+      <c r="J15" s="115"/>
+      <c r="K15" s="115"/>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="42"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="90" t="s">
+      <c r="A16" s="45"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="90"/>
-      <c r="E16" s="90"/>
-      <c r="F16" s="90"/>
-      <c r="G16" s="91"/>
-      <c r="H16" s="90" t="s">
+      <c r="D16" s="66"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="66"/>
+      <c r="G16" s="67"/>
+      <c r="H16" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="I16" s="90"/>
-      <c r="J16" s="90"/>
-      <c r="K16" s="99"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="66"/>
+      <c r="K16" s="50"/>
     </row>
     <row r="17" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="27"/>
+      <c r="B17" s="73"/>
       <c r="C17" s="65"/>
       <c r="D17" s="65"/>
       <c r="E17" s="65"/>
       <c r="F17" s="65"/>
       <c r="G17" s="65"/>
-      <c r="H17" s="92"/>
-      <c r="I17" s="93"/>
-      <c r="J17" s="93"/>
-      <c r="K17" s="99"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="50"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="27"/>
-      <c r="B18" s="27"/>
+      <c r="A18" s="73"/>
+      <c r="B18" s="73"/>
       <c r="C18" s="65"/>
       <c r="D18" s="65"/>
       <c r="E18" s="65"/>
       <c r="F18" s="65"/>
       <c r="G18" s="65"/>
-      <c r="H18" s="94"/>
+      <c r="H18" s="70"/>
       <c r="I18" s="65"/>
       <c r="J18" s="65"/>
-      <c r="K18" s="99"/>
+      <c r="K18" s="50"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="27"/>
-      <c r="B19" s="27"/>
+      <c r="A19" s="73"/>
+      <c r="B19" s="73"/>
       <c r="C19" s="65"/>
       <c r="D19" s="65"/>
       <c r="E19" s="65"/>
       <c r="F19" s="65"/>
       <c r="G19" s="65"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="96"/>
-      <c r="J19" s="96"/>
-      <c r="K19" s="99"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="72"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="50"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="27"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="60"/>
-      <c r="J20" s="60"/>
-      <c r="K20" s="99"/>
+      <c r="A20" s="73"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="95"/>
+      <c r="D20" s="95"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="95"/>
+      <c r="H20" s="95"/>
+      <c r="I20" s="95"/>
+      <c r="J20" s="95"/>
+      <c r="K20" s="50"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="73" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="61"/>
-      <c r="K21" s="61"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="73"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="96"/>
+      <c r="I21" s="96"/>
+      <c r="J21" s="96"/>
+      <c r="K21" s="96"/>
     </row>
     <row r="22" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="70" t="s">
+      <c r="A22" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="70"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="61"/>
-      <c r="J22" s="61"/>
-      <c r="K22" s="61"/>
+      <c r="B22" s="77"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="96"/>
+      <c r="I22" s="96"/>
+      <c r="J22" s="96"/>
+      <c r="K22" s="96"/>
     </row>
     <row r="23" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="71" t="s">
+      <c r="A23" s="78" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="71"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="61"/>
-      <c r="J23" s="61"/>
-      <c r="K23" s="61"/>
+      <c r="B23" s="78"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="96"/>
+      <c r="I23" s="96"/>
+      <c r="J23" s="96"/>
+      <c r="K23" s="96"/>
     </row>
     <row r="24" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="71" t="s">
+      <c r="A24" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="71"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="61"/>
-      <c r="I24" s="61"/>
-      <c r="J24" s="61"/>
-      <c r="K24" s="61"/>
+      <c r="B24" s="78"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="96"/>
+      <c r="I24" s="96"/>
+      <c r="J24" s="96"/>
+      <c r="K24" s="96"/>
     </row>
     <row r="25" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="71" t="s">
+      <c r="A25" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="71"/>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="61"/>
-      <c r="J25" s="61"/>
-      <c r="K25" s="61"/>
+      <c r="B25" s="78"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
+      <c r="H25" s="96"/>
+      <c r="I25" s="96"/>
+      <c r="J25" s="96"/>
+      <c r="K25" s="96"/>
     </row>
     <row r="26" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="69"/>
-      <c r="B26" s="69"/>
-      <c r="C26" s="69"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="61"/>
-      <c r="I26" s="61"/>
-      <c r="J26" s="61"/>
-      <c r="K26" s="61"/>
+      <c r="A26" s="103"/>
+      <c r="B26" s="103"/>
+      <c r="C26" s="103"/>
+      <c r="D26" s="103"/>
+      <c r="E26" s="103"/>
+      <c r="F26" s="103"/>
+      <c r="G26" s="103"/>
+      <c r="H26" s="96"/>
+      <c r="I26" s="96"/>
+      <c r="J26" s="96"/>
+      <c r="K26" s="96"/>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="73" t="s">
+      <c r="A27" s="81" t="s">
         <v>76</v>
       </c>
-      <c r="B27" s="73"/>
-      <c r="C27" s="66" t="s">
+      <c r="B27" s="81"/>
+      <c r="C27" s="100" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="66"/>
-      <c r="E27" s="66"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="63"/>
+      <c r="D27" s="100"/>
+      <c r="E27" s="100"/>
+      <c r="F27" s="100"/>
+      <c r="G27" s="100"/>
+      <c r="H27" s="74"/>
+      <c r="I27" s="75"/>
+      <c r="J27" s="97"/>
+      <c r="K27" s="98"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="73"/>
-      <c r="B28" s="73"/>
-      <c r="C28" s="66" t="s">
+      <c r="A28" s="81"/>
+      <c r="B28" s="81"/>
+      <c r="C28" s="100" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="66"/>
-      <c r="E28" s="66"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="66"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="63"/>
+      <c r="D28" s="100"/>
+      <c r="E28" s="100"/>
+      <c r="F28" s="100"/>
+      <c r="G28" s="100"/>
+      <c r="H28" s="74"/>
+      <c r="I28" s="75"/>
+      <c r="J28" s="97"/>
+      <c r="K28" s="98"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="73"/>
-      <c r="B29" s="73"/>
-      <c r="C29" s="67" t="s">
+      <c r="A29" s="81"/>
+      <c r="B29" s="81"/>
+      <c r="C29" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="67"/>
-      <c r="E29" s="67"/>
-      <c r="F29" s="67"/>
-      <c r="G29" s="67"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="62"/>
-      <c r="K29" s="63"/>
+      <c r="D29" s="101"/>
+      <c r="E29" s="101"/>
+      <c r="F29" s="101"/>
+      <c r="G29" s="101"/>
+      <c r="H29" s="93"/>
+      <c r="I29" s="94"/>
+      <c r="J29" s="97"/>
+      <c r="K29" s="98"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="73"/>
-      <c r="B30" s="73"/>
-      <c r="C30" s="68" t="s">
+      <c r="A30" s="81"/>
+      <c r="B30" s="81"/>
+      <c r="C30" s="102" t="s">
         <v>77</v>
       </c>
-      <c r="D30" s="68"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="68"/>
-      <c r="G30" s="68"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="62"/>
-      <c r="K30" s="63"/>
+      <c r="D30" s="102"/>
+      <c r="E30" s="102"/>
+      <c r="F30" s="102"/>
+      <c r="G30" s="102"/>
+      <c r="H30" s="93"/>
+      <c r="I30" s="94"/>
+      <c r="J30" s="97"/>
+      <c r="K30" s="98"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="73"/>
-      <c r="B31" s="73"/>
-      <c r="C31" s="68" t="s">
+      <c r="A31" s="81"/>
+      <c r="B31" s="81"/>
+      <c r="C31" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="D31" s="68"/>
-      <c r="E31" s="68"/>
-      <c r="F31" s="68"/>
-      <c r="G31" s="68"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="62"/>
-      <c r="K31" s="63"/>
+      <c r="D31" s="102"/>
+      <c r="E31" s="102"/>
+      <c r="F31" s="102"/>
+      <c r="G31" s="102"/>
+      <c r="H31" s="93"/>
+      <c r="I31" s="94"/>
+      <c r="J31" s="97"/>
+      <c r="K31" s="98"/>
     </row>
     <row r="32" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="73"/>
-      <c r="B32" s="73"/>
-      <c r="C32" s="68" t="s">
+      <c r="A32" s="81"/>
+      <c r="B32" s="81"/>
+      <c r="C32" s="102" t="s">
         <v>78</v>
       </c>
-      <c r="D32" s="68"/>
-      <c r="E32" s="68"/>
-      <c r="F32" s="68"/>
-      <c r="G32" s="68"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="62"/>
-      <c r="K32" s="63"/>
+      <c r="D32" s="102"/>
+      <c r="E32" s="102"/>
+      <c r="F32" s="102"/>
+      <c r="G32" s="102"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="94"/>
+      <c r="J32" s="97"/>
+      <c r="K32" s="98"/>
     </row>
     <row r="33" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="73"/>
-      <c r="B33" s="73"/>
-      <c r="C33" s="68" t="s">
+      <c r="A33" s="81"/>
+      <c r="B33" s="81"/>
+      <c r="C33" s="102" t="s">
         <v>18</v>
       </c>
-      <c r="D33" s="68"/>
-      <c r="E33" s="68"/>
-      <c r="F33" s="68"/>
-      <c r="G33" s="68"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="62"/>
-      <c r="K33" s="63"/>
+      <c r="D33" s="102"/>
+      <c r="E33" s="102"/>
+      <c r="F33" s="102"/>
+      <c r="G33" s="102"/>
+      <c r="H33" s="74"/>
+      <c r="I33" s="75"/>
+      <c r="J33" s="97"/>
+      <c r="K33" s="98"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="73"/>
-      <c r="B34" s="73"/>
-      <c r="C34" s="68" t="s">
+      <c r="A34" s="81"/>
+      <c r="B34" s="81"/>
+      <c r="C34" s="102" t="s">
         <v>19</v>
       </c>
-      <c r="D34" s="68"/>
-      <c r="E34" s="68"/>
-      <c r="F34" s="68"/>
-      <c r="G34" s="68"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="33"/>
-      <c r="J34" s="62"/>
-      <c r="K34" s="63"/>
+      <c r="D34" s="102"/>
+      <c r="E34" s="102"/>
+      <c r="F34" s="102"/>
+      <c r="G34" s="102"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94"/>
+      <c r="J34" s="97"/>
+      <c r="K34" s="98"/>
     </row>
     <row r="35" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="34"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="34"/>
-      <c r="K35" s="34"/>
+      <c r="A35" s="76"/>
+      <c r="B35" s="76"/>
+      <c r="C35" s="76"/>
+      <c r="D35" s="76"/>
+      <c r="E35" s="76"/>
+      <c r="F35" s="76"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
+      <c r="I35" s="76"/>
+      <c r="J35" s="76"/>
+      <c r="K35" s="76"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="75" t="s">
+      <c r="A36" s="86" t="s">
         <v>79</v>
       </c>
-      <c r="B36" s="76"/>
-      <c r="C36" s="80" t="s">
+      <c r="B36" s="87"/>
+      <c r="C36" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="D36" s="80"/>
-      <c r="E36" s="80"/>
-      <c r="F36" s="80"/>
-      <c r="G36" s="80"/>
-      <c r="H36" s="74" t="s">
+      <c r="D36" s="90"/>
+      <c r="E36" s="90"/>
+      <c r="F36" s="90"/>
+      <c r="G36" s="90"/>
+      <c r="H36" s="85" t="s">
         <v>80</v>
       </c>
-      <c r="I36" s="74"/>
-      <c r="J36" s="97"/>
-      <c r="K36" s="98"/>
+      <c r="I36" s="85"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="30"/>
     </row>
     <row r="37" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="77"/>
-      <c r="B37" s="27"/>
-      <c r="C37" s="80" t="s">
+      <c r="A37" s="88"/>
+      <c r="B37" s="73"/>
+      <c r="C37" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="D37" s="80"/>
-      <c r="E37" s="80"/>
-      <c r="F37" s="80"/>
-      <c r="G37" s="80"/>
-      <c r="H37" s="54" t="s">
+      <c r="D37" s="90"/>
+      <c r="E37" s="90"/>
+      <c r="F37" s="90"/>
+      <c r="G37" s="90"/>
+      <c r="H37" s="111" t="s">
         <v>67</v>
       </c>
-      <c r="I37" s="55"/>
-      <c r="J37" s="97"/>
-      <c r="K37" s="98"/>
+      <c r="I37" s="112"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="30"/>
     </row>
     <row r="38" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="77"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="37" t="s">
+      <c r="A38" s="88"/>
+      <c r="B38" s="73"/>
+      <c r="C38" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="39"/>
-      <c r="H38" s="40" t="s">
+      <c r="D38" s="83"/>
+      <c r="E38" s="83"/>
+      <c r="F38" s="83"/>
+      <c r="G38" s="84"/>
+      <c r="H38" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="I38" s="41"/>
-      <c r="J38" s="97"/>
-      <c r="K38" s="98"/>
+      <c r="I38" s="118"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="30"/>
     </row>
     <row r="39" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="77"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="80" t="s">
+      <c r="A39" s="88"/>
+      <c r="B39" s="73"/>
+      <c r="C39" s="90" t="s">
         <v>59</v>
       </c>
-      <c r="D39" s="80"/>
-      <c r="E39" s="80"/>
-      <c r="F39" s="80"/>
-      <c r="G39" s="80"/>
-      <c r="H39" s="40" t="s">
+      <c r="D39" s="90"/>
+      <c r="E39" s="90"/>
+      <c r="F39" s="90"/>
+      <c r="G39" s="90"/>
+      <c r="H39" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="I39" s="72"/>
-      <c r="J39" s="97"/>
-      <c r="K39" s="98"/>
+      <c r="I39" s="80"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="30"/>
       <c r="N39" s="15"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="77"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="81" t="s">
+      <c r="A40" s="88"/>
+      <c r="B40" s="73"/>
+      <c r="C40" s="91" t="s">
         <v>66</v>
       </c>
-      <c r="D40" s="80"/>
-      <c r="E40" s="80"/>
-      <c r="F40" s="80"/>
-      <c r="G40" s="80"/>
-      <c r="H40" s="40" t="s">
+      <c r="D40" s="90"/>
+      <c r="E40" s="90"/>
+      <c r="F40" s="90"/>
+      <c r="G40" s="90"/>
+      <c r="H40" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="I40" s="72"/>
-      <c r="J40" s="97"/>
-      <c r="K40" s="98"/>
+      <c r="I40" s="80"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="30"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="77"/>
-      <c r="B41" s="27"/>
-      <c r="C41" s="37" t="s">
+      <c r="A41" s="88"/>
+      <c r="B41" s="73"/>
+      <c r="C41" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="D41" s="38"/>
-      <c r="E41" s="38"/>
-      <c r="F41" s="38"/>
-      <c r="G41" s="39"/>
-      <c r="H41" s="40" t="s">
+      <c r="D41" s="83"/>
+      <c r="E41" s="83"/>
+      <c r="F41" s="83"/>
+      <c r="G41" s="84"/>
+      <c r="H41" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="I41" s="41"/>
-      <c r="J41" s="97"/>
-      <c r="K41" s="98"/>
+      <c r="I41" s="118"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="30"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="78"/>
-      <c r="B42" s="79"/>
-      <c r="C42" s="80" t="s">
+      <c r="A42" s="89"/>
+      <c r="B42" s="60"/>
+      <c r="C42" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="80"/>
-      <c r="E42" s="80"/>
-      <c r="F42" s="80"/>
-      <c r="G42" s="80"/>
-      <c r="H42" s="40" t="s">
+      <c r="D42" s="90"/>
+      <c r="E42" s="90"/>
+      <c r="F42" s="90"/>
+      <c r="G42" s="90"/>
+      <c r="H42" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="I42" s="72"/>
-      <c r="J42" s="97"/>
-      <c r="K42" s="98"/>
+      <c r="I42" s="80"/>
+      <c r="J42" s="29"/>
+      <c r="K42" s="30"/>
     </row>
     <row r="43" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="34"/>
-      <c r="B43" s="34"/>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="34"/>
-      <c r="F43" s="34"/>
-      <c r="G43" s="34"/>
-      <c r="H43" s="34"/>
-      <c r="I43" s="34"/>
-      <c r="J43" s="34"/>
-      <c r="K43" s="34"/>
+      <c r="A43" s="76"/>
+      <c r="B43" s="76"/>
+      <c r="C43" s="76"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="76"/>
+      <c r="I43" s="76"/>
+      <c r="J43" s="76"/>
+      <c r="K43" s="76"/>
     </row>
     <row r="44" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="27" t="s">
+      <c r="A44" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="25"/>
-      <c r="H44" s="25"/>
-      <c r="I44" s="25"/>
-      <c r="J44" s="25"/>
-      <c r="K44" s="25"/>
+      <c r="B44" s="73"/>
+      <c r="C44" s="73"/>
+      <c r="D44" s="105"/>
+      <c r="E44" s="105"/>
+      <c r="F44" s="105"/>
+      <c r="G44" s="105"/>
+      <c r="H44" s="105"/>
+      <c r="I44" s="105"/>
+      <c r="J44" s="105"/>
+      <c r="K44" s="105"/>
     </row>
     <row r="45" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="27" t="s">
+      <c r="A45" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="25"/>
-      <c r="I45" s="25"/>
-      <c r="J45" s="25"/>
-      <c r="K45" s="25"/>
+      <c r="B45" s="73"/>
+      <c r="C45" s="73"/>
+      <c r="D45" s="105"/>
+      <c r="E45" s="105"/>
+      <c r="F45" s="105"/>
+      <c r="G45" s="105"/>
+      <c r="H45" s="105"/>
+      <c r="I45" s="105"/>
+      <c r="J45" s="105"/>
+      <c r="K45" s="105"/>
     </row>
     <row r="46" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="27" t="s">
+      <c r="A46" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
-      <c r="H46" s="25"/>
-      <c r="I46" s="25"/>
-      <c r="J46" s="25"/>
-      <c r="K46" s="25"/>
+      <c r="B46" s="73"/>
+      <c r="C46" s="73"/>
+      <c r="D46" s="105"/>
+      <c r="E46" s="105"/>
+      <c r="F46" s="105"/>
+      <c r="G46" s="105"/>
+      <c r="H46" s="105"/>
+      <c r="I46" s="105"/>
+      <c r="J46" s="105"/>
+      <c r="K46" s="105"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="27" t="s">
+      <c r="A47" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="35" t="s">
+      <c r="B47" s="73"/>
+      <c r="C47" s="73"/>
+      <c r="D47" s="117" t="s">
         <v>82</v>
       </c>
-      <c r="E47" s="35"/>
-      <c r="F47" s="35"/>
-      <c r="G47" s="35"/>
-      <c r="H47" s="35"/>
-      <c r="I47" s="35"/>
-      <c r="J47" s="35"/>
-      <c r="K47" s="35"/>
+      <c r="E47" s="117"/>
+      <c r="F47" s="117"/>
+      <c r="G47" s="117"/>
+      <c r="H47" s="117"/>
+      <c r="I47" s="117"/>
+      <c r="J47" s="117"/>
+      <c r="K47" s="117"/>
     </row>
     <row r="48" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="B48" s="27"/>
-      <c r="C48" s="27"/>
-      <c r="D48" s="26" t="s">
+      <c r="B48" s="73"/>
+      <c r="C48" s="73"/>
+      <c r="D48" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="E48" s="26"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="26"/>
-      <c r="H48" s="26"/>
-      <c r="I48" s="26"/>
-      <c r="J48" s="26"/>
-      <c r="K48" s="26"/>
+      <c r="E48" s="114"/>
+      <c r="F48" s="114"/>
+      <c r="G48" s="114"/>
+      <c r="H48" s="114"/>
+      <c r="I48" s="114"/>
+      <c r="J48" s="114"/>
+      <c r="K48" s="114"/>
     </row>
     <row r="49" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="36" t="s">
+      <c r="A49" s="104" t="s">
         <v>20</v>
       </c>
-      <c r="B49" s="49" t="s">
+      <c r="B49" s="106" t="s">
         <v>86</v>
       </c>
-      <c r="C49" s="49"/>
-      <c r="D49" s="49"/>
-      <c r="E49" s="49"/>
-      <c r="F49" s="49"/>
-      <c r="G49" s="49"/>
-      <c r="H49" s="49"/>
-      <c r="I49" s="49"/>
-      <c r="J49" s="49"/>
-      <c r="K49" s="49"/>
+      <c r="C49" s="106"/>
+      <c r="D49" s="106"/>
+      <c r="E49" s="106"/>
+      <c r="F49" s="106"/>
+      <c r="G49" s="106"/>
+      <c r="H49" s="106"/>
+      <c r="I49" s="106"/>
+      <c r="J49" s="106"/>
+      <c r="K49" s="106"/>
     </row>
     <row r="50" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="36"/>
-      <c r="B50" s="49"/>
-      <c r="C50" s="49"/>
-      <c r="D50" s="49"/>
-      <c r="E50" s="49"/>
-      <c r="F50" s="49"/>
-      <c r="G50" s="49"/>
-      <c r="H50" s="49"/>
-      <c r="I50" s="49"/>
-      <c r="J50" s="49"/>
-      <c r="K50" s="49"/>
+      <c r="A50" s="104"/>
+      <c r="B50" s="106"/>
+      <c r="C50" s="106"/>
+      <c r="D50" s="106"/>
+      <c r="E50" s="106"/>
+      <c r="F50" s="106"/>
+      <c r="G50" s="106"/>
+      <c r="H50" s="106"/>
+      <c r="I50" s="106"/>
+      <c r="J50" s="106"/>
+      <c r="K50" s="106"/>
     </row>
     <row r="51" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="53" t="s">
+      <c r="A51" s="110" t="s">
         <v>87</v>
       </c>
-      <c r="B51" s="53"/>
-      <c r="C51" s="53"/>
-      <c r="D51" s="53"/>
-      <c r="E51" s="53"/>
-      <c r="F51" s="53"/>
-      <c r="G51" s="53"/>
-      <c r="H51" s="53"/>
-      <c r="I51" s="53"/>
-      <c r="J51" s="53"/>
-      <c r="K51" s="53"/>
+      <c r="B51" s="110"/>
+      <c r="C51" s="110"/>
+      <c r="D51" s="110"/>
+      <c r="E51" s="110"/>
+      <c r="F51" s="110"/>
+      <c r="G51" s="110"/>
+      <c r="H51" s="110"/>
+      <c r="I51" s="110"/>
+      <c r="J51" s="110"/>
+      <c r="K51" s="110"/>
     </row>
     <row r="52" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="107"/>
-      <c r="B52" s="108"/>
-      <c r="C52" s="108"/>
-      <c r="D52" s="108"/>
-      <c r="E52" s="109"/>
+      <c r="A52" s="24"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="25"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="26"/>
       <c r="F52" s="11" t="s">
         <v>53</v>
       </c>
@@ -5559,20 +5559,20 @@
       <c r="H52" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="I52" s="50" t="s">
+      <c r="I52" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="J52" s="51"/>
-      <c r="K52" s="52"/>
+      <c r="J52" s="108"/>
+      <c r="K52" s="109"/>
     </row>
     <row r="53" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="46" t="s">
+      <c r="A53" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="47"/>
-      <c r="C53" s="47"/>
-      <c r="D53" s="47"/>
-      <c r="E53" s="48"/>
+      <c r="B53" s="35"/>
+      <c r="C53" s="35"/>
+      <c r="D53" s="35"/>
+      <c r="E53" s="36"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
@@ -5581,13 +5581,13 @@
       <c r="K53" s="23"/>
     </row>
     <row r="54" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="46" t="s">
+      <c r="A54" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="B54" s="47"/>
-      <c r="C54" s="47"/>
-      <c r="D54" s="47"/>
-      <c r="E54" s="48"/>
+      <c r="B54" s="35"/>
+      <c r="C54" s="35"/>
+      <c r="D54" s="35"/>
+      <c r="E54" s="36"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
@@ -5596,13 +5596,13 @@
       <c r="K54" s="23"/>
     </row>
     <row r="55" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="46" t="s">
+      <c r="A55" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B55" s="47"/>
-      <c r="C55" s="47"/>
-      <c r="D55" s="47"/>
-      <c r="E55" s="48"/>
+      <c r="B55" s="35"/>
+      <c r="C55" s="35"/>
+      <c r="D55" s="35"/>
+      <c r="E55" s="36"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
@@ -5611,13 +5611,13 @@
       <c r="K55" s="23"/>
     </row>
     <row r="56" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="46" t="s">
+      <c r="A56" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="B56" s="47"/>
-      <c r="C56" s="47"/>
-      <c r="D56" s="47"/>
-      <c r="E56" s="48"/>
+      <c r="B56" s="35"/>
+      <c r="C56" s="35"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="36"/>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
@@ -5626,13 +5626,13 @@
       <c r="K56" s="23"/>
     </row>
     <row r="57" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="46" t="s">
+      <c r="A57" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="B57" s="47"/>
-      <c r="C57" s="47"/>
-      <c r="D57" s="47"/>
-      <c r="E57" s="48"/>
+      <c r="B57" s="35"/>
+      <c r="C57" s="35"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="36"/>
       <c r="F57" s="4"/>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
@@ -5641,13 +5641,13 @@
       <c r="K57" s="23"/>
     </row>
     <row r="58" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="46" t="s">
+      <c r="A58" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="B58" s="47"/>
-      <c r="C58" s="47"/>
-      <c r="D58" s="47"/>
-      <c r="E58" s="48"/>
+      <c r="B58" s="35"/>
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="36"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
@@ -5656,13 +5656,13 @@
       <c r="K58" s="23"/>
     </row>
     <row r="59" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="46" t="s">
+      <c r="A59" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B59" s="47"/>
-      <c r="C59" s="47"/>
-      <c r="D59" s="47"/>
-      <c r="E59" s="48"/>
+      <c r="B59" s="35"/>
+      <c r="C59" s="35"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="36"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
@@ -5671,13 +5671,13 @@
       <c r="K59" s="23"/>
     </row>
     <row r="60" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="46" t="s">
+      <c r="A60" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="B60" s="47"/>
-      <c r="C60" s="47"/>
-      <c r="D60" s="47"/>
-      <c r="E60" s="48"/>
+      <c r="B60" s="35"/>
+      <c r="C60" s="35"/>
+      <c r="D60" s="35"/>
+      <c r="E60" s="36"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
@@ -5686,13 +5686,13 @@
       <c r="K60" s="23"/>
     </row>
     <row r="61" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="46" t="s">
+      <c r="A61" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="B61" s="47"/>
-      <c r="C61" s="47"/>
-      <c r="D61" s="47"/>
-      <c r="E61" s="48"/>
+      <c r="B61" s="35"/>
+      <c r="C61" s="35"/>
+      <c r="D61" s="35"/>
+      <c r="E61" s="36"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
@@ -5701,113 +5701,113 @@
       <c r="K61" s="23"/>
     </row>
     <row r="62" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="56" t="s">
+      <c r="A62" s="113" t="s">
         <v>85</v>
       </c>
-      <c r="B62" s="56"/>
-      <c r="C62" s="56"/>
-      <c r="D62" s="56"/>
-      <c r="E62" s="56"/>
-      <c r="F62" s="56"/>
-      <c r="G62" s="56"/>
-      <c r="H62" s="56"/>
-      <c r="I62" s="56"/>
-      <c r="J62" s="56"/>
-      <c r="K62" s="56"/>
+      <c r="B62" s="113"/>
+      <c r="C62" s="113"/>
+      <c r="D62" s="113"/>
+      <c r="E62" s="113"/>
+      <c r="F62" s="113"/>
+      <c r="G62" s="113"/>
+      <c r="H62" s="113"/>
+      <c r="I62" s="113"/>
+      <c r="J62" s="113"/>
+      <c r="K62" s="113"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A63" s="36" t="s">
+      <c r="A63" s="104" t="s">
         <v>88</v>
       </c>
-      <c r="B63" s="36"/>
-      <c r="C63" s="36"/>
-      <c r="D63" s="57"/>
-      <c r="E63" s="57"/>
-      <c r="F63" s="57"/>
-      <c r="G63" s="57"/>
-      <c r="H63" s="57"/>
-      <c r="I63" s="57"/>
-      <c r="J63" s="57"/>
-      <c r="K63" s="57"/>
+      <c r="B63" s="104"/>
+      <c r="C63" s="104"/>
+      <c r="D63" s="49"/>
+      <c r="E63" s="49"/>
+      <c r="F63" s="49"/>
+      <c r="G63" s="49"/>
+      <c r="H63" s="49"/>
+      <c r="I63" s="49"/>
+      <c r="J63" s="49"/>
+      <c r="K63" s="49"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A64" s="113"/>
-      <c r="B64" s="113"/>
-      <c r="C64" s="113"/>
-      <c r="D64" s="58"/>
-      <c r="E64" s="58"/>
-      <c r="F64" s="58"/>
-      <c r="G64" s="58"/>
-      <c r="H64" s="58"/>
-      <c r="I64" s="58"/>
-      <c r="J64" s="58"/>
-      <c r="K64" s="58"/>
+      <c r="A64" s="33"/>
+      <c r="B64" s="33"/>
+      <c r="C64" s="33"/>
+      <c r="D64" s="92"/>
+      <c r="E64" s="92"/>
+      <c r="F64" s="92"/>
+      <c r="G64" s="92"/>
+      <c r="H64" s="92"/>
+      <c r="I64" s="92"/>
+      <c r="J64" s="92"/>
+      <c r="K64" s="92"/>
     </row>
     <row r="65" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="114" t="s">
+      <c r="A65" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="B65" s="114"/>
-      <c r="C65" s="114"/>
-      <c r="D65" s="24" t="s">
+      <c r="B65" s="37"/>
+      <c r="C65" s="37"/>
+      <c r="D65" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="E65" s="24"/>
-      <c r="F65" s="24"/>
-      <c r="G65" s="24"/>
-      <c r="H65" s="24"/>
-      <c r="I65" s="24"/>
-      <c r="J65" s="24"/>
-      <c r="K65" s="24"/>
+      <c r="E65" s="44"/>
+      <c r="F65" s="44"/>
+      <c r="G65" s="44"/>
+      <c r="H65" s="44"/>
+      <c r="I65" s="44"/>
+      <c r="J65" s="44"/>
+      <c r="K65" s="44"/>
       <c r="L65" s="10"/>
       <c r="M65" s="10"/>
     </row>
     <row r="66" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="112"/>
-      <c r="B66" s="112"/>
-      <c r="C66" s="112"/>
-      <c r="D66" s="24"/>
-      <c r="E66" s="24"/>
-      <c r="F66" s="24"/>
-      <c r="G66" s="24"/>
-      <c r="H66" s="24"/>
-      <c r="I66" s="24"/>
-      <c r="J66" s="24"/>
-      <c r="K66" s="24"/>
+      <c r="A66" s="31"/>
+      <c r="B66" s="31"/>
+      <c r="C66" s="31"/>
+      <c r="D66" s="44"/>
+      <c r="E66" s="44"/>
+      <c r="F66" s="44"/>
+      <c r="G66" s="44"/>
+      <c r="H66" s="44"/>
+      <c r="I66" s="44"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="44"/>
     </row>
     <row r="67" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="112"/>
-      <c r="B67" s="112"/>
-      <c r="C67" s="112"/>
-      <c r="D67" s="112"/>
-      <c r="E67" s="112"/>
-      <c r="F67" s="112"/>
-      <c r="G67" s="112"/>
-      <c r="H67" s="112"/>
-      <c r="I67" s="112"/>
-      <c r="J67" s="112"/>
-      <c r="K67" s="112"/>
+      <c r="A67" s="31"/>
+      <c r="B67" s="31"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="31"/>
+      <c r="E67" s="31"/>
+      <c r="F67" s="31"/>
+      <c r="G67" s="31"/>
+      <c r="H67" s="31"/>
+      <c r="I67" s="31"/>
+      <c r="J67" s="31"/>
+      <c r="K67" s="31"/>
     </row>
     <row r="68" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="86" t="s">
+      <c r="A68" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="B68" s="86"/>
-      <c r="C68" s="86"/>
-      <c r="D68" s="86"/>
-      <c r="E68" s="86"/>
-      <c r="F68" s="86"/>
-      <c r="G68" s="86"/>
-      <c r="H68" s="86"/>
-      <c r="I68" s="86"/>
-      <c r="J68" s="86"/>
-      <c r="K68" s="86"/>
+      <c r="B68" s="32"/>
+      <c r="C68" s="32"/>
+      <c r="D68" s="32"/>
+      <c r="E68" s="32"/>
+      <c r="F68" s="32"/>
+      <c r="G68" s="32"/>
+      <c r="H68" s="32"/>
+      <c r="I68" s="32"/>
+      <c r="J68" s="32"/>
+      <c r="K68" s="32"/>
     </row>
     <row r="69" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="79" t="s">
+      <c r="A69" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="B69" s="79"/>
+      <c r="B69" s="60"/>
       <c r="C69" s="17"/>
       <c r="D69" s="17"/>
       <c r="E69" s="17"/>
@@ -5823,184 +5823,184 @@
         <v>32</v>
       </c>
       <c r="B70" s="6"/>
-      <c r="C70" s="97"/>
-      <c r="D70" s="98"/>
-      <c r="E70" s="98"/>
-      <c r="F70" s="98"/>
-      <c r="G70" s="98"/>
-      <c r="H70" s="98"/>
-      <c r="I70" s="98"/>
-      <c r="J70" s="98"/>
-      <c r="K70" s="98"/>
+      <c r="C70" s="29"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
+      <c r="J70" s="30"/>
+      <c r="K70" s="30"/>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="12" t="s">
         <v>33</v>
       </c>
       <c r="B71" s="6"/>
-      <c r="C71" s="97"/>
-      <c r="D71" s="98"/>
-      <c r="E71" s="98"/>
-      <c r="F71" s="98"/>
-      <c r="G71" s="98"/>
-      <c r="H71" s="98"/>
-      <c r="I71" s="98"/>
-      <c r="J71" s="98"/>
-      <c r="K71" s="98"/>
+      <c r="C71" s="29"/>
+      <c r="D71" s="30"/>
+      <c r="E71" s="30"/>
+      <c r="F71" s="30"/>
+      <c r="G71" s="30"/>
+      <c r="H71" s="30"/>
+      <c r="I71" s="30"/>
+      <c r="J71" s="30"/>
+      <c r="K71" s="30"/>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="12" t="s">
         <v>34</v>
       </c>
       <c r="B72" s="6"/>
-      <c r="C72" s="97"/>
-      <c r="D72" s="98"/>
-      <c r="E72" s="98"/>
-      <c r="F72" s="98"/>
-      <c r="G72" s="98"/>
-      <c r="H72" s="98"/>
-      <c r="I72" s="98"/>
-      <c r="J72" s="98"/>
-      <c r="K72" s="98"/>
+      <c r="C72" s="29"/>
+      <c r="D72" s="30"/>
+      <c r="E72" s="30"/>
+      <c r="F72" s="30"/>
+      <c r="G72" s="30"/>
+      <c r="H72" s="30"/>
+      <c r="I72" s="30"/>
+      <c r="J72" s="30"/>
+      <c r="K72" s="30"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="12" t="s">
         <v>35</v>
       </c>
       <c r="B73" s="6"/>
-      <c r="C73" s="103" t="s">
+      <c r="C73" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="D73" s="103"/>
+      <c r="D73" s="38"/>
       <c r="E73" s="6"/>
-      <c r="F73" s="97"/>
-      <c r="G73" s="98"/>
-      <c r="H73" s="98"/>
-      <c r="I73" s="98"/>
-      <c r="J73" s="98"/>
-      <c r="K73" s="98"/>
+      <c r="F73" s="29"/>
+      <c r="G73" s="30"/>
+      <c r="H73" s="30"/>
+      <c r="I73" s="30"/>
+      <c r="J73" s="30"/>
+      <c r="K73" s="30"/>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="12" t="s">
         <v>89</v>
       </c>
       <c r="B74" s="6"/>
-      <c r="C74" s="103" t="s">
+      <c r="C74" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="D74" s="103"/>
+      <c r="D74" s="38"/>
       <c r="E74" s="6"/>
-      <c r="F74" s="97"/>
-      <c r="G74" s="98"/>
-      <c r="H74" s="98"/>
-      <c r="I74" s="98"/>
-      <c r="J74" s="98"/>
-      <c r="K74" s="98"/>
+      <c r="F74" s="29"/>
+      <c r="G74" s="30"/>
+      <c r="H74" s="30"/>
+      <c r="I74" s="30"/>
+      <c r="J74" s="30"/>
+      <c r="K74" s="30"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B75" s="82"/>
-      <c r="C75" s="83"/>
-      <c r="D75" s="83"/>
-      <c r="E75" s="84"/>
-      <c r="F75" s="97"/>
-      <c r="G75" s="98"/>
-      <c r="H75" s="98"/>
-      <c r="I75" s="98"/>
-      <c r="J75" s="98"/>
-      <c r="K75" s="98"/>
+      <c r="B75" s="46"/>
+      <c r="C75" s="47"/>
+      <c r="D75" s="47"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="29"/>
+      <c r="G75" s="30"/>
+      <c r="H75" s="30"/>
+      <c r="I75" s="30"/>
+      <c r="J75" s="30"/>
+      <c r="K75" s="30"/>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B76" s="82"/>
-      <c r="C76" s="83"/>
-      <c r="D76" s="83"/>
-      <c r="E76" s="84"/>
-      <c r="F76" s="97"/>
-      <c r="G76" s="98"/>
-      <c r="H76" s="98"/>
-      <c r="I76" s="98"/>
-      <c r="J76" s="98"/>
-      <c r="K76" s="98"/>
+      <c r="B76" s="46"/>
+      <c r="C76" s="47"/>
+      <c r="D76" s="47"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="29"/>
+      <c r="G76" s="30"/>
+      <c r="H76" s="30"/>
+      <c r="I76" s="30"/>
+      <c r="J76" s="30"/>
+      <c r="K76" s="30"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B77" s="82"/>
-      <c r="C77" s="83"/>
-      <c r="D77" s="83"/>
-      <c r="E77" s="84"/>
-      <c r="F77" s="97"/>
-      <c r="G77" s="98"/>
-      <c r="H77" s="98"/>
-      <c r="I77" s="98"/>
-      <c r="J77" s="98"/>
-      <c r="K77" s="98"/>
+      <c r="B77" s="46"/>
+      <c r="C77" s="47"/>
+      <c r="D77" s="47"/>
+      <c r="E77" s="48"/>
+      <c r="F77" s="29"/>
+      <c r="G77" s="30"/>
+      <c r="H77" s="30"/>
+      <c r="I77" s="30"/>
+      <c r="J77" s="30"/>
+      <c r="K77" s="30"/>
     </row>
     <row r="78" spans="1:13" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="98"/>
-      <c r="B78" s="98"/>
-      <c r="C78" s="98"/>
-      <c r="D78" s="98"/>
-      <c r="E78" s="98"/>
-      <c r="F78" s="98"/>
-      <c r="G78" s="98"/>
-      <c r="H78" s="98"/>
-      <c r="I78" s="98"/>
-      <c r="J78" s="98"/>
-      <c r="K78" s="98"/>
+      <c r="A78" s="30"/>
+      <c r="B78" s="30"/>
+      <c r="C78" s="30"/>
+      <c r="D78" s="30"/>
+      <c r="E78" s="30"/>
+      <c r="F78" s="30"/>
+      <c r="G78" s="30"/>
+      <c r="H78" s="30"/>
+      <c r="I78" s="30"/>
+      <c r="J78" s="30"/>
+      <c r="K78" s="30"/>
     </row>
     <row r="79" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B79" s="42"/>
-      <c r="C79" s="42"/>
-      <c r="D79" s="42"/>
-      <c r="E79" s="42"/>
-      <c r="F79" s="42"/>
-      <c r="G79" s="42"/>
-      <c r="H79" s="42"/>
-      <c r="I79" s="42"/>
-      <c r="J79" s="42"/>
-      <c r="K79" s="42"/>
+      <c r="B79" s="45"/>
+      <c r="C79" s="45"/>
+      <c r="D79" s="45"/>
+      <c r="E79" s="45"/>
+      <c r="F79" s="45"/>
+      <c r="G79" s="45"/>
+      <c r="H79" s="45"/>
+      <c r="I79" s="45"/>
+      <c r="J79" s="45"/>
+      <c r="K79" s="45"/>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="12" t="s">
         <v>40</v>
       </c>
       <c r="B80" s="6"/>
-      <c r="C80" s="103" t="s">
+      <c r="C80" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="D80" s="103"/>
-      <c r="E80" s="103"/>
-      <c r="F80" s="115"/>
-      <c r="G80" s="115"/>
-      <c r="H80" s="117"/>
-      <c r="I80" s="118"/>
-      <c r="J80" s="118"/>
-      <c r="K80" s="118"/>
+      <c r="D80" s="38"/>
+      <c r="E80" s="38"/>
+      <c r="F80" s="39"/>
+      <c r="G80" s="39"/>
+      <c r="H80" s="42"/>
+      <c r="I80" s="43"/>
+      <c r="J80" s="43"/>
+      <c r="K80" s="43"/>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="16" t="s">
         <v>42</v>
       </c>
       <c r="B81" s="6"/>
-      <c r="C81" s="116"/>
-      <c r="D81" s="100"/>
-      <c r="E81" s="100"/>
-      <c r="F81" s="100"/>
-      <c r="G81" s="100"/>
-      <c r="H81" s="100"/>
-      <c r="I81" s="100"/>
-      <c r="J81" s="100"/>
-      <c r="K81" s="100"/>
+      <c r="C81" s="40"/>
+      <c r="D81" s="41"/>
+      <c r="E81" s="41"/>
+      <c r="F81" s="41"/>
+      <c r="G81" s="41"/>
+      <c r="H81" s="41"/>
+      <c r="I81" s="41"/>
+      <c r="J81" s="41"/>
+      <c r="K81" s="41"/>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
@@ -6011,15 +6011,15 @@
         <v>44</v>
       </c>
       <c r="D82" s="6"/>
-      <c r="E82" s="102" t="s">
+      <c r="E82" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="F82" s="102"/>
+      <c r="F82" s="52"/>
       <c r="G82" s="6"/>
-      <c r="H82" s="105"/>
-      <c r="I82" s="106"/>
-      <c r="J82" s="106"/>
-      <c r="K82" s="106"/>
+      <c r="H82" s="58"/>
+      <c r="I82" s="59"/>
+      <c r="J82" s="59"/>
+      <c r="K82" s="59"/>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="12" t="s">
@@ -6030,17 +6030,17 @@
         <v>46</v>
       </c>
       <c r="D83" s="7"/>
-      <c r="E83" s="103" t="s">
+      <c r="E83" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="F83" s="103"/>
+      <c r="F83" s="38"/>
       <c r="G83" s="6"/>
-      <c r="H83" s="103" t="s">
+      <c r="H83" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="I83" s="103"/>
-      <c r="J83" s="104"/>
-      <c r="K83" s="104"/>
+      <c r="I83" s="38"/>
+      <c r="J83" s="53"/>
+      <c r="K83" s="53"/>
       <c r="L83" s="2"/>
       <c r="M83" s="13"/>
     </row>
@@ -6048,174 +6048,304 @@
       <c r="A84" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B84" s="43"/>
-      <c r="C84" s="44"/>
-      <c r="D84" s="45"/>
-      <c r="E84" s="110"/>
-      <c r="F84" s="111"/>
-      <c r="G84" s="111"/>
-      <c r="H84" s="111"/>
-      <c r="I84" s="111"/>
-      <c r="J84" s="111"/>
-      <c r="K84" s="111"/>
+      <c r="B84" s="55"/>
+      <c r="C84" s="56"/>
+      <c r="D84" s="57"/>
+      <c r="E84" s="27"/>
+      <c r="F84" s="28"/>
+      <c r="G84" s="28"/>
+      <c r="H84" s="28"/>
+      <c r="I84" s="28"/>
+      <c r="J84" s="28"/>
+      <c r="K84" s="28"/>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="B85" s="43"/>
-      <c r="C85" s="44"/>
-      <c r="D85" s="45"/>
-      <c r="E85" s="97"/>
-      <c r="F85" s="98"/>
-      <c r="G85" s="98"/>
-      <c r="H85" s="98"/>
-      <c r="I85" s="98"/>
-      <c r="J85" s="98"/>
-      <c r="K85" s="98"/>
+      <c r="B85" s="55"/>
+      <c r="C85" s="56"/>
+      <c r="D85" s="57"/>
+      <c r="E85" s="29"/>
+      <c r="F85" s="30"/>
+      <c r="G85" s="30"/>
+      <c r="H85" s="30"/>
+      <c r="I85" s="30"/>
+      <c r="J85" s="30"/>
+      <c r="K85" s="30"/>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B86" s="43"/>
-      <c r="C86" s="44"/>
-      <c r="D86" s="45"/>
-      <c r="E86" s="97"/>
-      <c r="F86" s="98"/>
-      <c r="G86" s="98"/>
-      <c r="H86" s="98"/>
-      <c r="I86" s="98"/>
-      <c r="J86" s="98"/>
-      <c r="K86" s="98"/>
+      <c r="B86" s="55"/>
+      <c r="C86" s="56"/>
+      <c r="D86" s="57"/>
+      <c r="E86" s="29"/>
+      <c r="F86" s="30"/>
+      <c r="G86" s="30"/>
+      <c r="H86" s="30"/>
+      <c r="I86" s="30"/>
+      <c r="J86" s="30"/>
+      <c r="K86" s="30"/>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A87" s="42"/>
-      <c r="B87" s="42"/>
-      <c r="C87" s="42"/>
-      <c r="D87" s="42"/>
-      <c r="E87" s="42"/>
-      <c r="F87" s="42"/>
-      <c r="G87" s="42"/>
-      <c r="H87" s="42"/>
-      <c r="I87" s="42"/>
-      <c r="J87" s="42"/>
-      <c r="K87" s="42"/>
+      <c r="A87" s="45"/>
+      <c r="B87" s="45"/>
+      <c r="C87" s="45"/>
+      <c r="D87" s="45"/>
+      <c r="E87" s="45"/>
+      <c r="F87" s="45"/>
+      <c r="G87" s="45"/>
+      <c r="H87" s="45"/>
+      <c r="I87" s="45"/>
+      <c r="J87" s="45"/>
+      <c r="K87" s="45"/>
     </row>
     <row r="88" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="59" t="s">
+      <c r="A88" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="B88" s="59"/>
-      <c r="C88" s="59"/>
-      <c r="D88" s="57" t="s">
+      <c r="B88" s="54"/>
+      <c r="C88" s="54"/>
+      <c r="D88" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="E88" s="57"/>
-      <c r="F88" s="57"/>
-      <c r="G88" s="57"/>
-      <c r="H88" s="57"/>
-      <c r="I88" s="57"/>
-      <c r="J88" s="57"/>
-      <c r="K88" s="57"/>
+      <c r="E88" s="49"/>
+      <c r="F88" s="49"/>
+      <c r="G88" s="49"/>
+      <c r="H88" s="49"/>
+      <c r="I88" s="49"/>
+      <c r="J88" s="49"/>
+      <c r="K88" s="49"/>
       <c r="L88" s="5"/>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A89" s="99"/>
-      <c r="B89" s="99"/>
-      <c r="C89" s="99"/>
-      <c r="D89" s="99"/>
-      <c r="E89" s="99"/>
-      <c r="F89" s="99"/>
-      <c r="G89" s="99"/>
-      <c r="H89" s="99"/>
-      <c r="I89" s="99"/>
-      <c r="J89" s="99"/>
-      <c r="K89" s="99"/>
+      <c r="A89" s="50"/>
+      <c r="B89" s="50"/>
+      <c r="C89" s="50"/>
+      <c r="D89" s="50"/>
+      <c r="E89" s="50"/>
+      <c r="F89" s="50"/>
+      <c r="G89" s="50"/>
+      <c r="H89" s="50"/>
+      <c r="I89" s="50"/>
+      <c r="J89" s="50"/>
+      <c r="K89" s="50"/>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A90" s="101" t="s">
+      <c r="A90" s="51" t="s">
         <v>91</v>
       </c>
-      <c r="B90" s="101"/>
-      <c r="C90" s="101"/>
-      <c r="D90" s="101"/>
-      <c r="E90" s="101"/>
-      <c r="F90" s="101"/>
-      <c r="G90" s="101"/>
-      <c r="H90" s="101"/>
-      <c r="I90" s="101"/>
-      <c r="J90" s="101"/>
-      <c r="K90" s="101"/>
+      <c r="B90" s="51"/>
+      <c r="C90" s="51"/>
+      <c r="D90" s="51"/>
+      <c r="E90" s="51"/>
+      <c r="F90" s="51"/>
+      <c r="G90" s="51"/>
+      <c r="H90" s="51"/>
+      <c r="I90" s="51"/>
+      <c r="J90" s="51"/>
+      <c r="K90" s="51"/>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A91" s="101"/>
-      <c r="B91" s="101"/>
-      <c r="C91" s="101"/>
-      <c r="D91" s="101"/>
-      <c r="E91" s="101"/>
-      <c r="F91" s="101"/>
-      <c r="G91" s="101"/>
-      <c r="H91" s="101"/>
-      <c r="I91" s="101"/>
-      <c r="J91" s="101"/>
-      <c r="K91" s="101"/>
+      <c r="A91" s="51"/>
+      <c r="B91" s="51"/>
+      <c r="C91" s="51"/>
+      <c r="D91" s="51"/>
+      <c r="E91" s="51"/>
+      <c r="F91" s="51"/>
+      <c r="G91" s="51"/>
+      <c r="H91" s="51"/>
+      <c r="I91" s="51"/>
+      <c r="J91" s="51"/>
+      <c r="K91" s="51"/>
     </row>
     <row r="92" spans="1:13" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="101"/>
-      <c r="B92" s="101"/>
-      <c r="C92" s="101"/>
-      <c r="D92" s="101"/>
-      <c r="E92" s="101"/>
-      <c r="F92" s="101"/>
-      <c r="G92" s="101"/>
-      <c r="H92" s="101"/>
-      <c r="I92" s="101"/>
-      <c r="J92" s="101"/>
-      <c r="K92" s="101"/>
+      <c r="A92" s="51"/>
+      <c r="B92" s="51"/>
+      <c r="C92" s="51"/>
+      <c r="D92" s="51"/>
+      <c r="E92" s="51"/>
+      <c r="F92" s="51"/>
+      <c r="G92" s="51"/>
+      <c r="H92" s="51"/>
+      <c r="I92" s="51"/>
+      <c r="J92" s="51"/>
+      <c r="K92" s="51"/>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A93" s="101"/>
-      <c r="B93" s="101"/>
-      <c r="C93" s="101"/>
-      <c r="D93" s="101"/>
-      <c r="E93" s="101"/>
-      <c r="F93" s="101"/>
-      <c r="G93" s="101"/>
-      <c r="H93" s="101"/>
-      <c r="I93" s="101"/>
-      <c r="J93" s="101"/>
-      <c r="K93" s="101"/>
+      <c r="A93" s="51"/>
+      <c r="B93" s="51"/>
+      <c r="C93" s="51"/>
+      <c r="D93" s="51"/>
+      <c r="E93" s="51"/>
+      <c r="F93" s="51"/>
+      <c r="G93" s="51"/>
+      <c r="H93" s="51"/>
+      <c r="I93" s="51"/>
+      <c r="J93" s="51"/>
+      <c r="K93" s="51"/>
     </row>
     <row r="94" spans="1:13" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="101"/>
-      <c r="B94" s="101"/>
-      <c r="C94" s="101"/>
-      <c r="D94" s="101"/>
-      <c r="E94" s="101"/>
-      <c r="F94" s="101"/>
-      <c r="G94" s="101"/>
-      <c r="H94" s="101"/>
-      <c r="I94" s="101"/>
-      <c r="J94" s="101"/>
-      <c r="K94" s="101"/>
+      <c r="A94" s="51"/>
+      <c r="B94" s="51"/>
+      <c r="C94" s="51"/>
+      <c r="D94" s="51"/>
+      <c r="E94" s="51"/>
+      <c r="F94" s="51"/>
+      <c r="G94" s="51"/>
+      <c r="H94" s="51"/>
+      <c r="I94" s="51"/>
+      <c r="J94" s="51"/>
+      <c r="K94" s="51"/>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A95" s="101"/>
-      <c r="B95" s="101"/>
-      <c r="C95" s="101"/>
-      <c r="D95" s="101"/>
-      <c r="E95" s="101"/>
-      <c r="F95" s="101"/>
-      <c r="G95" s="101"/>
-      <c r="H95" s="101"/>
-      <c r="I95" s="101"/>
-      <c r="J95" s="101"/>
-      <c r="K95" s="101"/>
+      <c r="A95" s="51"/>
+      <c r="B95" s="51"/>
+      <c r="C95" s="51"/>
+      <c r="D95" s="51"/>
+      <c r="E95" s="51"/>
+      <c r="F95" s="51"/>
+      <c r="G95" s="51"/>
+      <c r="H95" s="51"/>
+      <c r="I95" s="51"/>
+      <c r="J95" s="51"/>
+      <c r="K95" s="51"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="154">
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="D65:K65"/>
+    <mergeCell ref="D44:K44"/>
+    <mergeCell ref="D48:K48"/>
+    <mergeCell ref="A8:C11"/>
+    <mergeCell ref="D12:K12"/>
+    <mergeCell ref="D13:K13"/>
+    <mergeCell ref="D8:K11"/>
+    <mergeCell ref="D15:K15"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="D47:K47"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="D46:K46"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="D45:K45"/>
+    <mergeCell ref="B49:K50"/>
+    <mergeCell ref="I53:K53"/>
+    <mergeCell ref="I52:K52"/>
+    <mergeCell ref="A51:K51"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="A62:K62"/>
+    <mergeCell ref="D63:K63"/>
+    <mergeCell ref="D64:K64"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:K26"/>
+    <mergeCell ref="J27:K34"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="A27:B34"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="A36:B42"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="B76:E76"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="D5:K5"/>
+    <mergeCell ref="D6:K6"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:I1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="J36:K42"/>
+    <mergeCell ref="A17:B20"/>
+    <mergeCell ref="K16:K20"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="A87:K87"/>
+    <mergeCell ref="D88:K88"/>
+    <mergeCell ref="A89:K89"/>
+    <mergeCell ref="A90:K95"/>
+    <mergeCell ref="E82:F82"/>
+    <mergeCell ref="H83:I83"/>
+    <mergeCell ref="J83:K83"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="A88:C88"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="H82:K82"/>
     <mergeCell ref="I56:K56"/>
     <mergeCell ref="I55:K55"/>
     <mergeCell ref="I54:K54"/>
@@ -6240,136 +6370,6 @@
     <mergeCell ref="B79:K79"/>
     <mergeCell ref="B75:E75"/>
     <mergeCell ref="B77:E77"/>
-    <mergeCell ref="A87:K87"/>
-    <mergeCell ref="D88:K88"/>
-    <mergeCell ref="A89:K89"/>
-    <mergeCell ref="A90:K95"/>
-    <mergeCell ref="E82:F82"/>
-    <mergeCell ref="H83:I83"/>
-    <mergeCell ref="J83:K83"/>
-    <mergeCell ref="E83:F83"/>
-    <mergeCell ref="A88:C88"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="H82:K82"/>
-    <mergeCell ref="B76:E76"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="D5:K5"/>
-    <mergeCell ref="D6:K6"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:I1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="J36:K42"/>
-    <mergeCell ref="A17:B20"/>
-    <mergeCell ref="K16:K20"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="A35:K35"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="A27:B34"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="A36:B42"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="D64:K64"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:K26"/>
-    <mergeCell ref="J27:K34"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="D45:K45"/>
-    <mergeCell ref="B49:K50"/>
-    <mergeCell ref="I53:K53"/>
-    <mergeCell ref="I52:K52"/>
-    <mergeCell ref="A51:K51"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="A62:K62"/>
-    <mergeCell ref="D63:K63"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="D65:K65"/>
-    <mergeCell ref="D44:K44"/>
-    <mergeCell ref="D48:K48"/>
-    <mergeCell ref="A8:C11"/>
-    <mergeCell ref="D12:K12"/>
-    <mergeCell ref="D13:K13"/>
-    <mergeCell ref="D8:K11"/>
-    <mergeCell ref="D15:K15"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="A43:K43"/>
-    <mergeCell ref="D47:K47"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="D46:K46"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="A12:C12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.63936781609195403" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="92" orientation="portrait" r:id="rId1"/>
